--- a/public/downloads/HalldinAssessing2023.xlsx
+++ b/public/downloads/HalldinAssessing2023.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>N</t>
@@ -659,10 +682,10 @@
         <v>147</v>
       </c>
       <c r="N3" s="5">
-        <v>600.2773568630219</v>
+        <v>600277.3568630219</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03277517645989745</v>
+        <v>32.77517645989745</v>
       </c>
       <c r="P3" s="5">
         <v>18315</v>
@@ -709,10 +732,10 @@
         <v>147</v>
       </c>
       <c r="N4" s="5">
-        <v>881.7907953262329</v>
+        <v>881790.7953262329</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05014733822373936</v>
+        <v>50.14733822373936</v>
       </c>
       <c r="P4" s="5">
         <v>17584</v>
@@ -759,10 +782,10 @@
         <v>147</v>
       </c>
       <c r="N5" s="5">
-        <v>1442.834282636642</v>
+        <v>1442834.282636642</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1387073911398426</v>
+        <v>138.7073911398426</v>
       </c>
       <c r="P5" s="5">
         <v>10402</v>
@@ -809,10 +832,10 @@
         <v>147</v>
       </c>
       <c r="N6" s="5">
-        <v>1285.536293506622</v>
+        <v>1285536.293506622</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08392324673629863</v>
+        <v>83.92324673629862</v>
       </c>
       <c r="P6" s="5">
         <v>15318</v>
@@ -859,10 +882,10 @@
         <v>147</v>
       </c>
       <c r="N7" s="5">
-        <v>1512.777350187302</v>
+        <v>1512777.350187302</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1666421403599143</v>
+        <v>166.6421403599143</v>
       </c>
       <c r="P7" s="5">
         <v>9078</v>
@@ -909,10 +932,10 @@
         <v>147</v>
       </c>
       <c r="N8" s="5">
-        <v>125.0118548870087</v>
+        <v>125011.8548870087</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01265430254955043</v>
+        <v>12.65430254955043</v>
       </c>
       <c r="P8" s="5">
         <v>9879</v>
@@ -959,10 +982,10 @@
         <v>147</v>
       </c>
       <c r="N9" s="5">
-        <v>694.7569761276245</v>
+        <v>694756.9761276245</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02849817367929876</v>
+        <v>28.49817367929876</v>
       </c>
       <c r="P9" s="5">
         <v>24379</v>
@@ -1009,10 +1032,10 @@
         <v>147</v>
       </c>
       <c r="N10" s="5">
-        <v>925.1740863323212</v>
+        <v>925174.0863323212</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08487835654424965</v>
+        <v>84.87835654424964</v>
       </c>
       <c r="P10" s="5">
         <v>10900</v>
@@ -1059,10 +1082,10 @@
         <v>147</v>
       </c>
       <c r="N11" s="5">
-        <v>445.4149551391602</v>
+        <v>445414.9551391602</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04176417769706143</v>
+        <v>41.76417769706143</v>
       </c>
       <c r="P11" s="5">
         <v>10665</v>
@@ -1109,10 +1132,10 @@
         <v>147</v>
       </c>
       <c r="N12" s="5">
-        <v>213.2016212940216</v>
+        <v>213201.6212940216</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01861860285512371</v>
+        <v>18.61860285512371</v>
       </c>
       <c r="P12" s="5">
         <v>11451</v>
@@ -1159,10 +1182,10 @@
         <v>147</v>
       </c>
       <c r="N13" s="5">
-        <v>752.6523058414459</v>
+        <v>752652.3058414459</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07416024296398127</v>
+        <v>74.16024296398128</v>
       </c>
       <c r="P13" s="5">
         <v>10149</v>
@@ -1209,10 +1232,10 @@
         <v>63</v>
       </c>
       <c r="N14" s="5">
-        <v>230.7395882606506</v>
+        <v>230739.5882606506</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2352085507244145</v>
+        <v>235.2085507244145</v>
       </c>
       <c r="P14" s="5">
         <v>981</v>
@@ -1259,10 +1282,10 @@
         <v>63</v>
       </c>
       <c r="N15" s="5">
-        <v>1072.267245531082</v>
+        <v>1072267.245531082</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2359223862554636</v>
+        <v>235.9223862554636</v>
       </c>
       <c r="P15" s="5">
         <v>4545</v>
@@ -1309,10 +1332,10 @@
         <v>63</v>
       </c>
       <c r="N16" s="5">
-        <v>116.2981400489807</v>
+        <v>116298.1400489807</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1020159123236673</v>
+        <v>102.0159123236673</v>
       </c>
       <c r="P16" s="5">
         <v>1140</v>
@@ -1359,10 +1382,10 @@
         <v>63</v>
       </c>
       <c r="N17" s="5">
-        <v>460.4630789756775</v>
+        <v>460463.0789756775</v>
       </c>
       <c r="O17" s="4">
-        <v>0.100515843478646</v>
+        <v>100.515843478646</v>
       </c>
       <c r="P17" s="5">
         <v>4581</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,25 +1497,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1896614862562586</v>
+        <v>0.2817252312683258</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1896614862562586</v>
+        <v>0.2817252312683258</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1828575234438336</v>
+        <v>0.2631171164436286</v>
       </c>
       <c r="E3" s="4">
-        <v>85.04859086491743</v>
+        <v>89.10106899902823</v>
       </c>
       <c r="F3" s="4">
-        <v>90.25567273889425</v>
+        <v>92.78683285394695</v>
       </c>
       <c r="G3" s="5">
         <v>21</v>
@@ -1501,25 +1556,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2817252312683258</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0817321340879187</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0817321340879187</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4030111553364876</v>
+        <v>0.3462445676504636</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4030111553364876</v>
+        <v>0.3462445676504636</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3902363268409932</v>
+        <v>0.3283507517727292</v>
       </c>
       <c r="E4" s="4">
-        <v>84.84936831875611</v>
+        <v>88.09523809523812</v>
       </c>
       <c r="F4" s="4">
-        <v>91.27942899754981</v>
+        <v>91.84563758389261</v>
       </c>
       <c r="G4" s="5">
         <v>21</v>
@@ -1542,25 +1615,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3462445676504636</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1263278499545192</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1263278499545192</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2837744776324638</v>
+        <v>0.3439014478485071</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2837744776324638</v>
+        <v>0.3439014478485071</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2574208549399943</v>
+        <v>0.3276205732661119</v>
       </c>
       <c r="E5" s="4">
-        <v>84.93683187560741</v>
+        <v>88.92128279883386</v>
       </c>
       <c r="F5" s="4">
-        <v>89.52434217534883</v>
+        <v>92.05976350271649</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
@@ -1583,9 +1674,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3439014478485071</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1111906605412021</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1111906605412021</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,40 +1797,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2342818694066539</v>
+        <v>0.690500899396457</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2342818694066539</v>
+        <v>0.6425949009903889</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2213781373377839</v>
+        <v>0.6086632906347708</v>
       </c>
       <c r="E3" s="4">
-        <v>88.9698736637512</v>
+        <v>86.76060900550698</v>
       </c>
       <c r="F3" s="4">
-        <v>92.12687759667627</v>
+        <v>80.53052093320457</v>
       </c>
       <c r="G3" s="5">
         <v>21</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -1714,34 +1856,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.08438897697897119</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.678445331256604</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6531435231127602</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.425801647307318</v>
+        <v>0.5860253237146286</v>
       </c>
       <c r="C4" s="4">
-        <v>0.425801647307318</v>
+        <v>0.5486152785466402</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4269383362663489</v>
+        <v>0.6073517974956693</v>
       </c>
       <c r="E4" s="4">
-        <v>89.06705539358602</v>
+        <v>86.27955944282468</v>
       </c>
       <c r="F4" s="4">
-        <v>92.89016725258338</v>
+        <v>86.72632363907655</v>
       </c>
       <c r="G4" s="5">
         <v>21</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1755,40 +1915,58 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2069464945976506</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5917316215811991</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5649542160364217</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1679370507152357</v>
+        <v>0.5376720465487562</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1679370507152357</v>
+        <v>0.5469317438205508</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1494696017086556</v>
+        <v>0.7018568147229546</v>
       </c>
       <c r="E5" s="4">
-        <v>88.86783284742468</v>
+        <v>85.99449303530939</v>
       </c>
       <c r="F5" s="4">
-        <v>91.30446361989988</v>
+        <v>79.35602428890927</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
       </c>
       <c r="H5" s="5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -1796,9 +1974,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3846382373117194</v>
+      </c>
+      <c r="O5" s="5">
+        <v>16</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4250340783805768</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4231343004317978</v>
+      </c>
+      <c r="R5" s="5">
+        <v>16</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,25 +2097,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3098520144021244</v>
+        <v>0.1896614862562586</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3098520144021244</v>
+        <v>0.1896614862562586</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3078718232167635</v>
+        <v>0.1828575234438336</v>
       </c>
       <c r="E3" s="4">
-        <v>84.40395205701331</v>
+        <v>85.04859086491743</v>
       </c>
       <c r="F3" s="4">
-        <v>89.84819431128157</v>
+        <v>90.25567273889425</v>
       </c>
       <c r="G3" s="5">
         <v>21</v>
@@ -1927,25 +2156,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1492088850933464</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1847439409472504</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1847439409472504</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3169869082616753</v>
+        <v>0.4030111553364876</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3169869082616753</v>
+        <v>0.4030111553364876</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3168043931627402</v>
+        <v>0.3902363268409932</v>
       </c>
       <c r="E4" s="4">
-        <v>83.84029802397153</v>
+        <v>84.84936831875611</v>
       </c>
       <c r="F4" s="4">
-        <v>90.15873015873018</v>
+        <v>91.27942899754981</v>
       </c>
       <c r="G4" s="5">
         <v>21</v>
@@ -1968,25 +2215,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4030111553364876</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.147569540276464</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.147569540276464</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2201811125023163</v>
+        <v>0.2837744776324638</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2201811125023163</v>
+        <v>0.2837744776324638</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2134623407040462</v>
+        <v>0.2574208549399943</v>
       </c>
       <c r="E5" s="4">
-        <v>84.37641723356012</v>
+        <v>84.93683187560741</v>
       </c>
       <c r="F5" s="4">
-        <v>89.92755939064662</v>
+        <v>89.52434217534883</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
@@ -2009,9 +2274,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2837744776324638</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1298745465731394</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1298745465731394</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,25 +2397,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2759441981169012</v>
+        <v>0.2342818694066539</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2759441981169012</v>
+        <v>0.2342818694066539</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2413533861604048</v>
+        <v>0.2213781373377839</v>
       </c>
       <c r="E3" s="4">
-        <v>89.4460641399417</v>
+        <v>88.9698736637512</v>
       </c>
       <c r="F3" s="4">
-        <v>91.90156599552567</v>
+        <v>92.12687759667627</v>
       </c>
       <c r="G3" s="5">
         <v>21</v>
@@ -2140,25 +2456,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2095364948988953</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1774624521196545</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1774624521196545</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6680858771308392</v>
+        <v>0.425801647307318</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6680858771308392</v>
+        <v>0.425801647307318</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6357000510199994</v>
+        <v>0.4269383362663489</v>
       </c>
       <c r="E4" s="4">
-        <v>88.80466472303209</v>
+        <v>89.06705539358602</v>
       </c>
       <c r="F4" s="4">
-        <v>91.744966442953</v>
+        <v>92.89016725258338</v>
       </c>
       <c r="G4" s="5">
         <v>21</v>
@@ -2181,25 +2515,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.425801647307318</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1666338849942625</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1666338849942625</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2039191130970721</v>
+        <v>0.1679370507152357</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2039191130970721</v>
+        <v>0.1679370507152357</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1742652514121368</v>
+        <v>0.1494696017086556</v>
       </c>
       <c r="E5" s="4">
-        <v>89.65986394557825</v>
+        <v>88.86783284742468</v>
       </c>
       <c r="F5" s="4">
-        <v>91.52285075103862</v>
+        <v>91.30446361989988</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
@@ -2222,9 +2574,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.139255728204305</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1328640190651574</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1328640190651574</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,25 +2697,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.07403957529008394</v>
+        <v>0.3098520144021244</v>
       </c>
       <c r="C3" s="4">
-        <v>0.07403957529008394</v>
+        <v>0.3098520144021244</v>
       </c>
       <c r="D3" s="4">
-        <v>0.07960214186563316</v>
+        <v>0.3078718232167635</v>
       </c>
       <c r="E3" s="4">
-        <v>99.75218658892128</v>
+        <v>84.40395205701331</v>
       </c>
       <c r="F3" s="4">
-        <v>99.39011398742943</v>
+        <v>89.84819431128157</v>
       </c>
       <c r="G3" s="5">
         <v>21</v>
@@ -2353,25 +2756,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2906030806213191</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.165706514706096</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.165706514706096</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4387619336748194</v>
+        <v>0.3169869082616753</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4387619336748194</v>
+        <v>0.3169869082616753</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4307949952018817</v>
+        <v>0.3168043931627402</v>
       </c>
       <c r="E4" s="4">
-        <v>99.83965014577259</v>
+        <v>83.84029802397153</v>
       </c>
       <c r="F4" s="4">
-        <v>99.80345158197505</v>
+        <v>90.15873015873018</v>
       </c>
       <c r="G4" s="5">
         <v>21</v>
@@ -2394,25 +2815,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3169869082616753</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1447883219057045</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1447883219057045</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.087309201722319</v>
+        <v>0.2201811125023163</v>
       </c>
       <c r="C5" s="4">
-        <v>1.087309201722319</v>
+        <v>0.2201811125023163</v>
       </c>
       <c r="D5" s="4">
-        <v>1.091963450277815</v>
+        <v>0.2134623407040462</v>
       </c>
       <c r="E5" s="4">
-        <v>99.81049562682216</v>
+        <v>84.37641723356012</v>
       </c>
       <c r="F5" s="4">
-        <v>99.66442953020135</v>
+        <v>89.92755939064662</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
@@ -2435,9 +2874,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1986550151102295</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1238184829194417</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1238184829194417</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2997,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4904923679738746</v>
+        <v>0.2759441981169012</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4904923679738746</v>
+        <v>0.2759441981169012</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4864355538028515</v>
+        <v>0.2413533861604048</v>
       </c>
       <c r="E3" s="4">
-        <v>83.21671525753159</v>
+        <v>89.4460641399417</v>
       </c>
       <c r="F3" s="4">
-        <v>89.75071907957813</v>
+        <v>91.90156599552567</v>
       </c>
       <c r="G3" s="5">
         <v>21</v>
@@ -2566,25 +3056,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2759441981169012</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09052099576647564</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09052099576647564</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.121189833852918</v>
+        <v>0.6680858771308392</v>
       </c>
       <c r="C4" s="4">
-        <v>1.121189833852918</v>
+        <v>0.6680858771308392</v>
       </c>
       <c r="D4" s="4">
-        <v>1.147250534269484</v>
+        <v>0.6357000510199994</v>
       </c>
       <c r="E4" s="4">
-        <v>83.28312277291872</v>
+        <v>88.80466472303209</v>
       </c>
       <c r="F4" s="4">
-        <v>90.60083093640141</v>
+        <v>91.744966442953</v>
       </c>
       <c r="G4" s="5">
         <v>21</v>
@@ -2607,25 +3115,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.6680858771308392</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1072095773116682</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1072095773116682</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9777455558599115</v>
+        <v>0.2039191130970721</v>
       </c>
       <c r="C5" s="4">
-        <v>0.9777455558599115</v>
+        <v>0.2039191130970721</v>
       </c>
       <c r="D5" s="4">
-        <v>0.9749591749558481</v>
+        <v>0.1742652514121368</v>
       </c>
       <c r="E5" s="4">
-        <v>83.36410754778103</v>
+        <v>89.65986394557825</v>
       </c>
       <c r="F5" s="4">
-        <v>89.93395120911902</v>
+        <v>91.52285075103862</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
@@ -2648,9 +3174,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.201939560282058</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1039982127614597</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1039982127614597</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3297,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.06858449786938352</v>
+        <v>0.07403957529008394</v>
       </c>
       <c r="C3" s="4">
-        <v>0.06858449786938352</v>
+        <v>0.07403957529008394</v>
       </c>
       <c r="D3" s="4">
-        <v>0.07269012891247244</v>
+        <v>0.07960214186563316</v>
       </c>
       <c r="E3" s="4">
-        <v>99.54324586977648</v>
+        <v>99.75218658892128</v>
       </c>
       <c r="F3" s="4">
-        <v>99.28038777032066</v>
+        <v>99.39011398742943</v>
       </c>
       <c r="G3" s="5">
         <v>21</v>
@@ -2779,25 +3356,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.05496184664349493</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05452408630578993</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05452408630578993</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3530166728457966</v>
+        <v>0.4387619336748194</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3530166728457966</v>
+        <v>0.4387619336748194</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3436009327872658</v>
+        <v>0.4307949952018817</v>
       </c>
       <c r="E4" s="4">
-        <v>99.79105928085519</v>
+        <v>99.83965014577259</v>
       </c>
       <c r="F4" s="4">
-        <v>99.67987642484286</v>
+        <v>99.80345158197505</v>
       </c>
       <c r="G4" s="5">
         <v>21</v>
@@ -2820,25 +3415,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4387619336748194</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05045366858788035</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05045366858788035</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6054670727188761</v>
+        <v>1.087309201722319</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6054670727188761</v>
+        <v>1.087309201722319</v>
       </c>
       <c r="D5" s="4">
-        <v>0.605401836854333</v>
+        <v>1.091963450277815</v>
       </c>
       <c r="E5" s="4">
-        <v>99.71331389698737</v>
+        <v>99.81049562682216</v>
       </c>
       <c r="F5" s="4">
-        <v>99.4753382337275</v>
+        <v>99.66442953020135</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
@@ -2861,9 +3474,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-1.087309201722319</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04660824603209819</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04660824603209819</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,25 +3597,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3495831304528413</v>
+        <v>0.4904923679738746</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3495831304528413</v>
+        <v>0.4904923679738746</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3495894620271857</v>
+        <v>0.4864355538028515</v>
       </c>
       <c r="E3" s="4">
-        <v>83.37544541626178</v>
+        <v>83.21671525753159</v>
       </c>
       <c r="F3" s="4">
-        <v>90.11025886864815</v>
+        <v>89.75071907957813</v>
       </c>
       <c r="G3" s="5">
         <v>21</v>
@@ -2992,25 +3656,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4904923679738746</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04407739536125482</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04407739536125482</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8996905270379059</v>
+        <v>1.121189833852918</v>
       </c>
       <c r="C4" s="4">
-        <v>0.8996905270379059</v>
+        <v>1.121189833852918</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8931308258449585</v>
+        <v>1.147250534269484</v>
       </c>
       <c r="E4" s="4">
-        <v>82.86686103012637</v>
+        <v>83.28312277291872</v>
       </c>
       <c r="F4" s="4">
-        <v>90.46074358154894</v>
+        <v>90.60083093640141</v>
       </c>
       <c r="G4" s="5">
         <v>21</v>
@@ -3033,25 +3715,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-1.121189833852918</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05048050464603226</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05048050464603226</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7414357493540732</v>
+        <v>0.9777455558599115</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7414357493540732</v>
+        <v>0.9777455558599115</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7407462087635192</v>
+        <v>0.9749591749558481</v>
       </c>
       <c r="E5" s="4">
-        <v>83.48720440557179</v>
+        <v>83.36410754778103</v>
       </c>
       <c r="F5" s="4">
-        <v>90.11345477788431</v>
+        <v>89.93395120911902</v>
       </c>
       <c r="G5" s="5">
         <v>21</v>
@@ -3074,9 +3774,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.9777455558599115</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04224607941338646</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04224607941338646</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.06858449786938352</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.06858449786938352</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.07269012891247244</v>
+      </c>
+      <c r="E3" s="4">
+        <v>99.54324586977648</v>
+      </c>
+      <c r="F3" s="4">
+        <v>99.28038777032066</v>
+      </c>
+      <c r="G3" s="5">
+        <v>21</v>
+      </c>
+      <c r="H3" s="5">
+        <v>21</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.04990016770032044</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0664267984807265</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0664267984807265</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3530166728457966</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3530166728457966</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3436009327872658</v>
+      </c>
+      <c r="E4" s="4">
+        <v>99.79105928085519</v>
+      </c>
+      <c r="F4" s="4">
+        <v>99.67987642484286</v>
+      </c>
+      <c r="G4" s="5">
+        <v>21</v>
+      </c>
+      <c r="H4" s="5">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3530166728457966</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06004147120502834</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06004147120502834</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6054670727188761</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6054670727188761</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.605401836854333</v>
+      </c>
+      <c r="E5" s="4">
+        <v>99.71331389698737</v>
+      </c>
+      <c r="F5" s="4">
+        <v>99.4753382337275</v>
+      </c>
+      <c r="G5" s="5">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.6054670727188761</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0553493964411377</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0553493964411377</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3495831304528413</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3495831304528413</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3495894620271857</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.37544541626178</v>
+      </c>
+      <c r="F3" s="4">
+        <v>90.11025886864815</v>
+      </c>
+      <c r="G3" s="5">
+        <v>21</v>
+      </c>
+      <c r="H3" s="5">
+        <v>21</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3495831304528413</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06019478866140215</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06019478866140215</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.8996905270379059</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.8996905270379059</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.8931308258449585</v>
+      </c>
+      <c r="E4" s="4">
+        <v>82.86686103012637</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.46074358154894</v>
+      </c>
+      <c r="G4" s="5">
+        <v>21</v>
+      </c>
+      <c r="H4" s="5">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.8996905270379059</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1511123031849596</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1511123031849596</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.7414357493540732</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.7414357493540732</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.7407462087635192</v>
+      </c>
+      <c r="E5" s="4">
+        <v>83.48720440557179</v>
+      </c>
+      <c r="F5" s="4">
+        <v>90.11345477788431</v>
+      </c>
+      <c r="G5" s="5">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.7414357493540732</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1062115397551919</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1062115397551919</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>97.95918367346938</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.040816326530612</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.6802721088435374</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2252965426999499</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2193532026599798</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.2182690530296449</v>
+      </c>
+      <c r="K3" s="4">
+        <v>87.62784025174689</v>
+      </c>
+      <c r="L3" s="4">
+        <v>90.72775418892417</v>
+      </c>
+      <c r="M3" s="5">
+        <v>147</v>
+      </c>
+      <c r="N3" s="5">
+        <v>600277.3568630219</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.77517645989745</v>
+      </c>
+      <c r="P3" s="5">
+        <v>18315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>98.63945578231292</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.2610733228194766</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2541386104424925</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2557630330433468</v>
+      </c>
+      <c r="K4" s="4">
+        <v>83.8935165903096</v>
+      </c>
+      <c r="L4" s="4">
+        <v>87.6515393629482</v>
+      </c>
+      <c r="M4" s="5">
+        <v>147</v>
+      </c>
+      <c r="N4" s="5">
+        <v>881790.7953262329</v>
+      </c>
+      <c r="O4" s="4">
+        <v>50.14733822373936</v>
+      </c>
+      <c r="P4" s="5">
+        <v>17584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1163175579480297</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1163175579480297</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1189694121114055</v>
+      </c>
+      <c r="K5" s="4">
+        <v>86.76384839650147</v>
+      </c>
+      <c r="L5" s="4">
+        <v>91.56728910803696</v>
+      </c>
+      <c r="M5" s="5">
+        <v>147</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1442834.282636642</v>
+      </c>
+      <c r="O5" s="4">
+        <v>138.7073911398426</v>
+      </c>
+      <c r="P5" s="5">
+        <v>10402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>97.27891156462584</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.72108843537415</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4330119602447645</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.4415731123453916</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.4215517853782033</v>
+      </c>
+      <c r="K6" s="4">
+        <v>86.406127076681</v>
+      </c>
+      <c r="L6" s="4">
+        <v>87.73980733232811</v>
+      </c>
+      <c r="M6" s="5">
+        <v>147</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1285536.293506622</v>
+      </c>
+      <c r="O6" s="4">
+        <v>83.92324673629862</v>
+      </c>
+      <c r="P6" s="5">
+        <v>15318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.06502745818958097</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.06502745818958097</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.06307721495674733</v>
+      </c>
+      <c r="K7" s="4">
+        <v>90.19297514924337</v>
+      </c>
+      <c r="L7" s="4">
+        <v>93.39375123651251</v>
+      </c>
+      <c r="M7" s="5">
+        <v>147</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1512777.350187302</v>
+      </c>
+      <c r="O7" s="4">
+        <v>166.6421403599143</v>
+      </c>
+      <c r="P7" s="5">
+        <v>9078</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1104007461964896</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1104007461964896</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1035869772590076</v>
+      </c>
+      <c r="K8" s="4">
+        <v>88.55685131195335</v>
+      </c>
+      <c r="L8" s="4">
+        <v>91.84358307081224</v>
+      </c>
+      <c r="M8" s="5">
+        <v>147</v>
+      </c>
+      <c r="N8" s="5">
+        <v>125011.8548870087</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.65430254955043</v>
+      </c>
+      <c r="P8" s="5">
+        <v>9879</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>85.03401360544217</v>
+      </c>
+      <c r="C9" s="3">
+        <v>12.24489795918367</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.72108843537415</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.6193847993200852</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.6059951320621862</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.6108195030995138</v>
+      </c>
+      <c r="K9" s="4">
+        <v>86.71363783608689</v>
+      </c>
+      <c r="L9" s="4">
+        <v>83.67757841391455</v>
+      </c>
+      <c r="M9" s="5">
+        <v>147</v>
+      </c>
+      <c r="N9" s="5">
+        <v>694756.9761276245</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.49817367929876</v>
+      </c>
+      <c r="P9" s="5">
+        <v>24379</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.130156970983135</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.130156970983135</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1306189192248253</v>
+      </c>
+      <c r="K10" s="4">
+        <v>84.48146605581007</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.83944360742062</v>
+      </c>
+      <c r="M10" s="5">
+        <v>147</v>
+      </c>
+      <c r="N10" s="5">
+        <v>925174.0863323212</v>
+      </c>
+      <c r="O10" s="4">
+        <v>84.87835654424964</v>
+      </c>
+      <c r="P10" s="5">
+        <v>10900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1548327009790921</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1548327009790921</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1549461995244514</v>
+      </c>
+      <c r="K11" s="4">
+        <v>88.79726040075899</v>
+      </c>
+      <c r="L11" s="4">
+        <v>91.54415681261314</v>
+      </c>
+      <c r="M11" s="5">
+        <v>147</v>
+      </c>
+      <c r="N11" s="5">
+        <v>445414.9551391602</v>
+      </c>
+      <c r="O11" s="4">
+        <v>41.76417769706143</v>
+      </c>
+      <c r="P11" s="5">
+        <v>10665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.1765663303650827</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1765663303650827</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.170024703694253</v>
+      </c>
+      <c r="K12" s="4">
+        <v>83.60821879772318</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.38379826203413</v>
+      </c>
+      <c r="M12" s="5">
+        <v>147</v>
+      </c>
+      <c r="N12" s="5">
+        <v>213201.6212940216</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.61860285512371</v>
+      </c>
+      <c r="P12" s="5">
+        <v>11451</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1138069475361001</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1138069475361001</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1108427809478156</v>
+      </c>
+      <c r="K13" s="4">
+        <v>88.98931000971815</v>
+      </c>
+      <c r="L13" s="4">
+        <v>91.42727784626153</v>
+      </c>
+      <c r="M13" s="5">
+        <v>147</v>
+      </c>
+      <c r="N13" s="5">
+        <v>752652.3058414459</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74.16024296398128</v>
+      </c>
+      <c r="P13" s="5">
+        <v>10149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.05052866697525616</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.05052866697525616</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.04947418249439253</v>
+      </c>
+      <c r="K14" s="4">
+        <v>99.80077745383868</v>
+      </c>
+      <c r="L14" s="4">
+        <v>99.61933169986861</v>
+      </c>
+      <c r="M14" s="5">
+        <v>63</v>
+      </c>
+      <c r="N14" s="5">
+        <v>230739.5882606506</v>
+      </c>
+      <c r="O14" s="4">
+        <v>235.2085507244145</v>
+      </c>
+      <c r="P14" s="5">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.04560132647355785</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.04560132647355785</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.05350470496288633</v>
+      </c>
+      <c r="K15" s="4">
+        <v>83.28798185941045</v>
+      </c>
+      <c r="L15" s="4">
+        <v>90.09516707503285</v>
+      </c>
+      <c r="M15" s="5">
+        <v>63</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1072267.245531082</v>
+      </c>
+      <c r="O15" s="4">
+        <v>235.9223862554636</v>
+      </c>
+      <c r="P15" s="5">
+        <v>4545</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.06060588870896418</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.06060588870896418</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.06006339163100722</v>
+      </c>
+      <c r="K16" s="4">
+        <v>99.68253968253968</v>
+      </c>
+      <c r="L16" s="4">
+        <v>99.4785341429637</v>
+      </c>
+      <c r="M16" s="5">
+        <v>63</v>
+      </c>
+      <c r="N16" s="5">
+        <v>116298.1400489807</v>
+      </c>
+      <c r="O16" s="4">
+        <v>102.0159123236673</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1058395438671845</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1058395438671845</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1097540532516864</v>
+      </c>
+      <c r="K17" s="4">
+        <v>83.24317028398663</v>
+      </c>
+      <c r="L17" s="4">
+        <v>90.22815240936046</v>
+      </c>
+      <c r="M17" s="5">
+        <v>63</v>
+      </c>
+      <c r="N17" s="5">
+        <v>460463.0789756775</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.515843478646</v>
+      </c>
+      <c r="P17" s="5">
+        <v>4581</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -3250,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -3470,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L9" s="5">
         <v>0</v>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>144</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>145</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>147</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>143</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>147</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>147</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>125</v>
+      </c>
+      <c r="C9" s="5">
+        <v>18</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>2</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>147</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>147</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>147</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>147</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>63</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>63</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>63</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>63</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6864,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2743576038223442</v>
@@ -3960,10 +6923,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1473065351059631</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2636727300083986</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2700317152063144</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2961990379595331</v>
@@ -4001,10 +6982,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2783512002247984</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.210038401068467</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.210038401068467</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2278370787351464</v>
@@ -4042,9 +7041,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1929949580423584</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1834802757878352</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1834802757878352</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7164,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2870793571550859</v>
@@ -4173,10 +7223,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1085561100833729</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2580569743870867</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2416313448771689</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3742292399138456</v>
@@ -4214,10 +7282,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.333894418564991</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2662974777833407</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2662974777833407</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2851417687977248</v>
@@ -4255,9 +7341,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2794720106401309</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1492185972853645</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1492185972853645</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7372,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7391,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7433,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7464,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2609191539907312</v>
@@ -4386,10 +7523,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2609191539907312</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1008216812066278</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1008216812066278</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.403410697723129</v>
@@ -4427,10 +7582,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.403410697723129</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1278174185172165</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1278174185172165</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.405525635204824</v>
@@ -4468,9 +7641,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.405525635204824</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1010176013225147</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1010176013225147</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7672,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7691,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7733,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7764,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5212118753139899</v>
@@ -4599,10 +7823,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3965587318560115</v>
+      </c>
+      <c r="O3" s="5">
+        <v>19</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4557396290434453</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4908298578066881</v>
+      </c>
+      <c r="R3" s="5">
+        <v>19</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5583302174927667</v>
@@ -4640,10 +7882,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.489901140788182</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4429066733726011</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4429066733726011</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.347157916122385</v>
@@ -4681,9 +7941,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1187355179381917</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.341503843839614</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.341503843839614</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7972,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7991,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8033,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8064,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.211933260108275</v>
@@ -4812,10 +8123,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.211933260108275</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06132590571033521</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06132590571033521</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3550391946822249</v>
@@ -4853,10 +8182,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3550391946822249</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04791037629576519</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04791037629576519</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3444579216915632</v>
@@ -4894,9 +8241,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3444579216915632</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0516454961710589</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0516454961710589</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8272,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2817252312683258</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2817252312683258</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2631171164436286</v>
-      </c>
-      <c r="E3" s="4">
-        <v>89.10106899902823</v>
-      </c>
-      <c r="F3" s="4">
-        <v>92.78683285394695</v>
-      </c>
-      <c r="G3" s="5">
-        <v>21</v>
-      </c>
-      <c r="H3" s="5">
-        <v>21</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3462445676504636</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3462445676504636</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3283507517727292</v>
-      </c>
-      <c r="E4" s="4">
-        <v>88.09523809523812</v>
-      </c>
-      <c r="F4" s="4">
-        <v>91.84563758389261</v>
-      </c>
-      <c r="G4" s="5">
-        <v>21</v>
-      </c>
-      <c r="H4" s="5">
-        <v>21</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3439014478485071</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3439014478485071</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3276205732661119</v>
-      </c>
-      <c r="E5" s="4">
-        <v>88.92128279883386</v>
-      </c>
-      <c r="F5" s="4">
-        <v>92.05976350271649</v>
-      </c>
-      <c r="G5" s="5">
-        <v>21</v>
-      </c>
-      <c r="H5" s="5">
-        <v>21</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.690500899396457</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6425949009903889</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6086632906347708</v>
-      </c>
-      <c r="E3" s="4">
-        <v>86.76060900550698</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.53052093320457</v>
-      </c>
-      <c r="G3" s="5">
-        <v>21</v>
-      </c>
-      <c r="H3" s="5">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5">
-        <v>4</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5860253237146286</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5486152785466402</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6073517974956693</v>
-      </c>
-      <c r="E4" s="4">
-        <v>86.27955944282468</v>
-      </c>
-      <c r="F4" s="4">
-        <v>86.72632363907655</v>
-      </c>
-      <c r="G4" s="5">
-        <v>21</v>
-      </c>
-      <c r="H4" s="5">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5376720465487562</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5469317438205508</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7018568147229546</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.99449303530939</v>
-      </c>
-      <c r="F5" s="4">
-        <v>79.35602428890927</v>
-      </c>
-      <c r="G5" s="5">
-        <v>21</v>
-      </c>
-      <c r="H5" s="5">
-        <v>16</v>
-      </c>
-      <c r="I5" s="5">
-        <v>4</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/HalldinAssessing2023.xlsx
+++ b/public/downloads/HalldinAssessing2023.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2817252312683258</v>
+        <v>-0.258246114346008</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0817321340879187</v>
+        <v>0.08061408090114165</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0817321340879187</v>
+        <v>0.08061408090114165</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3462445676504636</v>
+        <v>-0.376442722407063</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1263278499545192</v>
+        <v>0.1248898425851573</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1263278499545192</v>
+        <v>0.1248898425851573</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3439014478485071</v>
+        <v>-0.3162798898129537</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1111906605412021</v>
+        <v>0.1061465709164844</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1111906605412021</v>
+        <v>0.1061465709164844</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -1857,22 +1857,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08438897697897119</v>
+        <v>0.08308634759305278</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.678445331256604</v>
+        <v>0.7098395015415181</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6531435231127602</v>
+        <v>0.550097524493079</v>
       </c>
       <c r="R3" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2069464945976506</v>
+        <v>0.009017243253765628</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5917316215811991</v>
+        <v>0.5864547162505221</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5649542160364217</v>
+        <v>0.5486152785466402</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3846382373117194</v>
+        <v>0.4860559213266242</v>
       </c>
       <c r="O5" s="5">
         <v>16</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4250340783805768</v>
+        <v>0.4082223705762382</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4231343004317978</v>
+        <v>0.4074075391895349</v>
       </c>
       <c r="R5" s="5">
         <v>16</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1492088850933464</v>
+        <v>-0.08315057434742812</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1847439409472504</v>
+        <v>0.1796244111661996</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1847439409472504</v>
+        <v>0.1796244111661996</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4030111553364876</v>
+        <v>-0.3741537031146436</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.147569540276464</v>
+        <v>0.1448178903356945</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.147569540276464</v>
+        <v>0.1448178903356945</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2837744776324638</v>
+        <v>-0.2522302076671417</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1298745465731394</v>
+        <v>0.1261456955255216</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1298745465731394</v>
+        <v>0.1261456955255216</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2095364948988953</v>
+        <v>-0.2120759260724299</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1774624521196545</v>
+        <v>0.1773415268256767</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1774624521196545</v>
+        <v>0.1773415268256767</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.425801647307318</v>
+        <v>-0.4971684850461315</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1666338849942625</v>
+        <v>0.1604239364927967</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1666338849942625</v>
+        <v>0.1604239364927967</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.139255728204305</v>
+        <v>-0.1367043123755138</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1328640190651574</v>
+        <v>0.1327425230733102</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1328640190651574</v>
+        <v>0.1327425230733102</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2906030806213191</v>
+        <v>-0.3159617437049747</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.165706514706096</v>
+        <v>0.16449895932116</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.165706514706096</v>
+        <v>0.16449895932116</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3169869082616753</v>
+        <v>-0.2456306356471032</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1447883219057045</v>
+        <v>0.1387562928735168</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1447883219057045</v>
+        <v>0.1387562928735168</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1986550151102295</v>
+        <v>-0.1941846334811999</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1238184829194417</v>
+        <v>0.1236056076037736</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1238184829194417</v>
+        <v>0.1236056076037736</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2759441981169012</v>
+        <v>-0.282471882950631</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09052099576647564</v>
+        <v>0.09021015363153613</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09052099576647564</v>
+        <v>0.09021015363153613</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6680858771308392</v>
+        <v>-0.6925130846793763</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1072095773116682</v>
+        <v>0.1060463769522141</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1072095773116682</v>
+        <v>0.1060463769522141</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.201939560282058</v>
+        <v>-0.1959614263032563</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1039982127614597</v>
+        <v>0.1037135397148502</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1039982127614597</v>
+        <v>0.1037135397148502</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05496184664349493</v>
+        <v>-0.05348507112654488</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05452408630578993</v>
+        <v>0.05445376366212564</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05452408630578993</v>
+        <v>0.05445376366212564</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4387619336748194</v>
+        <v>-0.4522594857989475</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05045366858788035</v>
+        <v>0.04981092801054091</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05045366858788035</v>
+        <v>0.04981092801054091</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.087309201722319</v>
+        <v>-1.083134839413106</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.04660824603209819</v>
+        <v>0.04640946687451661</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04660824603209819</v>
+        <v>0.04640946687451661</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4904923679738746</v>
+        <v>-0.4950864120037295</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04407739536125482</v>
+        <v>0.04385863135983316</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04407739536125482</v>
+        <v>0.04385863135983316</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.121189833852918</v>
+        <v>-1.133792189328277</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05048050464603226</v>
+        <v>0.04881572507744433</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05048050464603226</v>
+        <v>0.04881572507744433</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.9777455558599115</v>
+        <v>-0.9771560827793735</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.04224607941338646</v>
+        <v>0.04221800926669417</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04224607941338646</v>
+        <v>0.04221800926669417</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04990016770032044</v>
+        <v>-0.02451719543021369</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0664267984807265</v>
+        <v>0.06313036671607702</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0664267984807265</v>
+        <v>0.06313036671607702</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3530166728457966</v>
+        <v>-0.3363628076185421</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06004147120502834</v>
+        <v>0.05924843000373051</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06004147120502834</v>
+        <v>0.05924843000373051</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6054670727188761</v>
+        <v>-0.6035077483975062</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.0553493964411377</v>
+        <v>0.05511424927230692</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0553493964411377</v>
+        <v>0.05511424927230692</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3495831304528413</v>
+        <v>-0.3493372321681854</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06019478866140215</v>
+        <v>0.0601830792192757</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06019478866140215</v>
+        <v>0.0601830792192757</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.8996905270379059</v>
+        <v>-0.9200355696375766</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1511123031849596</v>
+        <v>0.1494021946384075</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1511123031849596</v>
+        <v>0.1494021946384075</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7414357493540732</v>
+        <v>-0.6915929058741312</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1062115397551919</v>
+        <v>0.09518025241760639</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1062115397551919</v>
+        <v>0.09518025241760639</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2252965426999499</v>
+        <v>0.2153192084216015</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2193532026599798</v>
+        <v>0.2093059833160724</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2182690530296449</v>
+        <v>0.2115757274368661</v>
       </c>
       <c r="K3" s="4">
         <v>87.62784025174689</v>
@@ -4571,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2610733228194766</v>
+        <v>0.2502113183925473</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2541386104424925</v>
+        <v>0.2430674182497977</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2557630330433468</v>
+        <v>0.2596914233149031</v>
       </c>
       <c r="K4" s="4">
         <v>83.8935165903096</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1163175579480297</v>
+        <v>0.1137797538424505</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1163175579480297</v>
+        <v>0.1137797538424505</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1189694121114055</v>
+        <v>0.1165535498016374</v>
       </c>
       <c r="K5" s="4">
         <v>86.76384839650147</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4330119602447645</v>
+        <v>0.4221423273082691</v>
       </c>
       <c r="I6" s="4">
-        <v>0.4415731123453916</v>
+        <v>0.4308399256718528</v>
       </c>
       <c r="J6" s="4">
-        <v>0.4215517853782033</v>
+        <v>0.4094893191980185</v>
       </c>
       <c r="K6" s="4">
         <v>86.406127076681</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.06502745818958097</v>
+        <v>0.06354526949871797</v>
       </c>
       <c r="I7" s="4">
-        <v>0.06502745818958097</v>
+        <v>0.06354526949871797</v>
       </c>
       <c r="J7" s="4">
-        <v>0.06307721495674733</v>
+        <v>0.06160736501263019</v>
       </c>
       <c r="K7" s="4">
         <v>90.19297514924337</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1104007461964896</v>
+        <v>0.1068477556582441</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1104007461964896</v>
+        <v>0.1068477556582441</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1035869772590076</v>
+        <v>0.102336974267718</v>
       </c>
       <c r="K8" s="4">
         <v>88.55685131195335</v>
@@ -4803,13 +4803,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>85.03401360544217</v>
+        <v>82.31292517006803</v>
       </c>
       <c r="C9" s="3">
         <v>12.24489795918367</v>
       </c>
       <c r="D9" s="3">
-        <v>2.72108843537415</v>
+        <v>5.442176870748299</v>
       </c>
       <c r="E9" s="3">
         <v>1.360544217687075</v>
@@ -4818,16 +4818,16 @@
         <v>1.360544217687075</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>2.72108843537415</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6193847993200852</v>
+        <v>0.6003181912920332</v>
       </c>
       <c r="I9" s="4">
-        <v>0.6059951320621862</v>
+        <v>0.5251179667772274</v>
       </c>
       <c r="J9" s="4">
-        <v>0.6108195030995138</v>
+        <v>0.5959475646221628</v>
       </c>
       <c r="K9" s="4">
         <v>86.71363783608689</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.130156970983135</v>
+        <v>0.1268237832950784</v>
       </c>
       <c r="I10" s="4">
-        <v>0.130156970983135</v>
+        <v>0.1268237832950784</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1306189192248253</v>
+        <v>0.1264200947154805</v>
       </c>
       <c r="K10" s="4">
         <v>84.48146605581007</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1548327009790921</v>
+        <v>0.1527277446964908</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1548327009790921</v>
+        <v>0.1527277446964908</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1549461995244514</v>
+        <v>0.1537311329170456</v>
       </c>
       <c r="K11" s="4">
         <v>88.79726040075899</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.1765663303650827</v>
+        <v>0.1682803976458623</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1765663303650827</v>
+        <v>0.1682803976458623</v>
       </c>
       <c r="J12" s="4">
-        <v>0.170024703694253</v>
+        <v>0.1620149108700828</v>
       </c>
       <c r="K12" s="4">
         <v>83.60821879772318</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1138069475361001</v>
+        <v>0.1069752070576635</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1138069475361001</v>
+        <v>0.1069752070576635</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1108427809478156</v>
+        <v>0.1078968575351189</v>
       </c>
       <c r="K13" s="4">
         <v>88.98931000971815</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.05052866697525616</v>
+        <v>0.05022471951572773</v>
       </c>
       <c r="I14" s="4">
-        <v>0.05052866697525616</v>
+        <v>0.05022471951572773</v>
       </c>
       <c r="J14" s="4">
-        <v>0.04947418249439253</v>
+        <v>0.05002088399925476</v>
       </c>
       <c r="K14" s="4">
         <v>99.80077745383868</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.04560132647355785</v>
+        <v>0.04496412190132389</v>
       </c>
       <c r="I15" s="4">
-        <v>0.04560132647355785</v>
+        <v>0.04496412190132389</v>
       </c>
       <c r="J15" s="4">
-        <v>0.05350470496288633</v>
+        <v>0.05226228266560001</v>
       </c>
       <c r="K15" s="4">
         <v>83.28798185941045</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.06060588870896418</v>
+        <v>0.05916434866403815</v>
       </c>
       <c r="I16" s="4">
-        <v>0.06060588870896418</v>
+        <v>0.05916434866403815</v>
       </c>
       <c r="J16" s="4">
-        <v>0.06006339163100722</v>
+        <v>0.05891814889452582</v>
       </c>
       <c r="K16" s="4">
         <v>99.68253968253968</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1058395438671845</v>
+        <v>0.1015885087584299</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1058395438671845</v>
+        <v>0.1015885087584299</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1097540532516864</v>
+        <v>0.1055336358879799</v>
       </c>
       <c r="K17" s="4">
         <v>83.24317028398663</v>
@@ -6374,13 +6374,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C9" s="5">
         <v>18</v>
       </c>
       <c r="D9" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E9" s="5">
         <v>2</v>
@@ -6389,7 +6389,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="5">
         <v>2</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1473065351059631</v>
+        <v>-0.1274379817114095</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2636727300083986</v>
+        <v>0.2617332147139158</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2700317152063144</v>
+        <v>0.2689886518168351</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -6983,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2783512002247984</v>
+        <v>-0.3023961471189978</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.210038401068467</v>
+        <v>0.2088934035973147</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.210038401068467</v>
+        <v>0.2088934035973147</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -7042,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1929949580423584</v>
+        <v>-0.1366093034448568</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1834802757878352</v>
+        <v>0.1807952446165256</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1834802757878352</v>
+        <v>0.1807952446165256</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -7224,13 +7224,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1085561100833729</v>
+        <v>-0.1254994547198294</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2580569743870867</v>
+        <v>0.2572501484520173</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2416313448771689</v>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.333894418564991</v>
+        <v>-0.3594979680783581</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2662974777833407</v>
+        <v>0.265078261139847</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2662974777833407</v>
+        <v>0.265078261139847</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -7342,16 +7342,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2794720106401309</v>
+        <v>-0.2306709650874836</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1492185972853645</v>
+        <v>0.1384169848499282</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1492185972853645</v>
+        <v>0.1384169848499282</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -7524,16 +7524,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2609191539907312</v>
+        <v>-0.2258161273493897</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1008216812066278</v>
+        <v>0.09875398906400992</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1008216812066278</v>
+        <v>0.09875398906400992</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -7583,16 +7583,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.403410697723129</v>
+        <v>-0.396544444054598</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1278174185172165</v>
+        <v>0.1274904540568102</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1278174185172165</v>
+        <v>0.1274904540568102</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -7642,16 +7642,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.405525635204824</v>
+        <v>-0.4151604385988321</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1010176013225147</v>
+        <v>0.1005588011608952</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1010176013225147</v>
+        <v>0.1005588011608952</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -7824,16 +7824,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3965587318560115</v>
+        <v>-0.3298462880775332</v>
       </c>
       <c r="O3" s="5">
         <v>19</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4557396290434453</v>
+        <v>0.446483593781609</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4908298578066881</v>
+        <v>0.4873186765551892</v>
       </c>
       <c r="R3" s="5">
         <v>19</v>
@@ -7883,16 +7883,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.489901140788182</v>
+        <v>-0.3310248876514379</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4429066733726011</v>
+        <v>0.4320675071351053</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4429066733726011</v>
+        <v>0.4320675071351053</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -7942,16 +7942,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1187355179381917</v>
+        <v>-0.1232322180148913</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.341503843839614</v>
+        <v>0.3412897152645331</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.341503843839614</v>
+        <v>0.3412897152645331</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -8124,16 +8124,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.211933260108275</v>
+        <v>-0.2078789724037051</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06132590571033521</v>
+        <v>0.06110810833516076</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06132590571033521</v>
+        <v>0.06110810833516076</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -8183,16 +8183,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3550391946822249</v>
+        <v>-0.3572287833376322</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04791037629576519</v>
+        <v>0.04780611016931722</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04791037629576519</v>
+        <v>0.04780611016931722</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -8242,16 +8242,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3444579216915632</v>
+        <v>-0.3370986358786467</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.0516454961710589</v>
+        <v>0.05116244973621741</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0516454961710589</v>
+        <v>0.05116244973621741</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
